--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136348819</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136342863</v>
       </c>
       <c r="B7" t="n">
-        <v>57866</v>
+        <v>57868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136342762</v>
       </c>
       <c r="B10" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136342763</v>
       </c>
       <c r="B19" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>136342764</v>
       </c>
       <c r="B25" t="n">
-        <v>58868</v>
+        <v>58870</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136348778</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136348820</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>136339655</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>136341916</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>136342257</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136342456</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>136342923</v>
       </c>
       <c r="B36" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136338975</v>
       </c>
       <c r="B41" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -1250,7 +1250,7 @@
         <v>136342863</v>
       </c>
       <c r="B7" t="n">
-        <v>57868</v>
+        <v>57881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -1250,7 +1250,7 @@
         <v>136342863</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27915-2026 artfynd.xlsx
+++ b/artfynd/A 27915-2026 artfynd.xlsx
@@ -1280,11 +1280,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
